--- a/ELITE_GYMNASTICS_2026-02-22_Girls_results.xlsx
+++ b/ELITE_GYMNASTICS_2026-02-22_Girls_results.xlsx
@@ -5,54 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mandbt-my.sharepoint.com/personal/cat_mandbt_onmicrosoft_com/Documents/NGL/22 Feb 2026 N Ireland Floor &amp; Vault/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mandbt-my.sharepoint.com/personal/cat_mandbt_onmicrosoft_com/Documents/NGL/22n/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{61043646-09B8-442F-BF30-8CE38152DAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F77EDE95-1D1D-4A02-857B-E5676A5C4D93}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{517A37E3-AB39-4020-80C5-ABE8D2611A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B76C3EF-A790-470A-975F-70C7FAC57BB2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{26B28785-DA53-49DF-83DF-E8362DAC667B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Vault" sheetId="2" r:id="rId1"/>
-    <sheet name="Floor" sheetId="1" r:id="rId2"/>
+    <sheet name="Vault" sheetId="6" r:id="rId1"/>
+    <sheet name="Uneven Bars" sheetId="5" r:id="rId2"/>
+    <sheet name="Floor" sheetId="4" r:id="rId3"/>
+    <sheet name="Balance Beam" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="42">
-  <si>
-    <t>BG Number</t>
-  </si>
-  <si>
-    <t>Club</t>
-  </si>
-  <si>
-    <t>Age Category</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Score</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="50">
   <si>
     <t>Country</t>
   </si>
@@ -60,64 +31,64 @@
     <t>Region</t>
   </si>
   <si>
-    <t>Training Hours</t>
+    <t>FinalScore</t>
+  </si>
+  <si>
+    <t>Club</t>
+  </si>
+  <si>
+    <t>AgeCategory</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>TrainingHrs</t>
   </si>
   <si>
     <t>Pro-Star Gymnastics Academy (91164)</t>
   </si>
   <si>
-    <t>6-8</t>
+    <t>9-11</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>11.900</t>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>Elite Gymnastics Academy (91978)</t>
+  </si>
+  <si>
+    <t>12-14</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>6-10</t>
+  </si>
+  <si>
+    <t>15+</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Rathgael Gymnastics &amp; Tumbling Club (40334)</t>
+  </si>
+  <si>
+    <t>6-8</t>
   </si>
   <si>
     <t>Great Britain</t>
   </si>
   <si>
-    <t>N. Ireland</t>
+    <t>Northern Ireland</t>
   </si>
   <si>
-    <t>2-5hrs</t>
-  </si>
-  <si>
-    <t>11.500</t>
-  </si>
-  <si>
-    <t>Elite Gymnastics Academy (91978)</t>
-  </si>
-  <si>
-    <t>11.300</t>
-  </si>
-  <si>
-    <t>11.200</t>
-  </si>
-  <si>
-    <t>11.100</t>
-  </si>
-  <si>
-    <t>11.000</t>
-  </si>
-  <si>
-    <t>9.700</t>
-  </si>
-  <si>
-    <t>9-11</t>
-  </si>
-  <si>
-    <t>12.000</t>
-  </si>
-  <si>
-    <t>11.800</t>
-  </si>
-  <si>
-    <t>11.400</t>
-  </si>
-  <si>
-    <t>12-14</t>
+    <t>Member ID</t>
   </si>
   <si>
     <t>Gender</t>
@@ -126,56 +97,100 @@
     <t>Girls</t>
   </si>
   <si>
+    <t>MemberID</t>
+  </si>
+  <si>
+    <t>9.600</t>
+  </si>
+  <si>
+    <t>11.100</t>
+  </si>
+  <si>
+    <t>7.900</t>
+  </si>
+  <si>
+    <t>9.500</t>
+  </si>
+  <si>
+    <t>10.000</t>
+  </si>
+  <si>
+    <t>12.200</t>
+  </si>
+  <si>
+    <t>10.900</t>
+  </si>
+  <si>
     <t>9.800</t>
+  </si>
+  <si>
+    <t>7.700</t>
+  </si>
+  <si>
+    <t>11.300</t>
+  </si>
+  <si>
+    <t>10.600</t>
+  </si>
+  <si>
+    <t>11.200</t>
+  </si>
+  <si>
+    <t>10.100</t>
+  </si>
+  <si>
+    <t>10.300</t>
+  </si>
+  <si>
+    <t>10.700</t>
+  </si>
+  <si>
+    <t>11.900</t>
+  </si>
+  <si>
+    <t>10.800</t>
+  </si>
+  <si>
+    <t>9.100</t>
   </si>
   <si>
     <t>9.200</t>
   </si>
   <si>
-    <t>9.000</t>
+    <t>9.700</t>
   </si>
   <si>
-    <t>8.900</t>
+    <t>8.500</t>
   </si>
   <si>
-    <t>8.700</t>
+    <t>9.900</t>
   </si>
   <si>
     <t>8.600</t>
   </si>
   <si>
-    <t>8.500</t>
-  </si>
-  <si>
-    <t>8.000</t>
-  </si>
-  <si>
-    <t>10.000</t>
-  </si>
-  <si>
-    <t>9.900</t>
-  </si>
-  <si>
-    <t>9.300</t>
-  </si>
-  <si>
     <t>8.800</t>
   </si>
   <si>
-    <t>9.600</t>
+    <t>11.700</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -186,10 +201,36 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -198,14 +239,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -292,7 +339,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -327,7 +373,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -362,16 +407,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -493,138 +542,94 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A6D7123-1ECE-48D5-901F-6EDE01C0106B}">
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CAEA4CF-2EFD-4C09-BA5B-547D68C8FE10}">
+  <dimension ref="A1:I45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="36.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="42.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.90625" customWidth="1"/>
+    <col min="6" max="6" width="14.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>27</v>
+      <c r="I1" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>3999212</v>
+        <v>4296363</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>9.1999999999999993</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>4460076</v>
+        <v>5208077</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>9.1999999999999993</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -633,30 +638,30 @@
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>4553029</v>
+        <v>3520989</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>8.8000000000000007</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -665,24 +670,24 @@
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>4826169</v>
+        <v>4035279</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>8.9</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
@@ -691,85 +696,85 @@
         <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>4613005</v>
+        <v>4033723</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>4667047</v>
+        <v>2811296</v>
       </c>
       <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>11.2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
-      </c>
       <c r="H7" t="s">
         <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>4489643</v>
+        <v>2716334</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>9.1</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -781,140 +786,140 @@
         <v>14</v>
       </c>
       <c r="I8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>4034048</v>
+        <v>4280394</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>8.8000000000000007</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>5212942</v>
+        <v>5140263</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D10">
+        <v>8.8000000000000007</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I10" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>4276592</v>
+        <v>3815749</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>11.1</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s">
         <v>14</v>
       </c>
       <c r="I11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>4300522</v>
+        <v>4795407</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D12">
+        <v>9.1</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I12" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>3635296</v>
+        <v>4571894</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D13">
+        <v>10.6</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
@@ -923,85 +928,85 @@
         <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>4001669</v>
+        <v>4286124</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D14">
+        <v>8.4</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I14" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>4718808</v>
+        <v>5105760</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D15">
+        <v>8.8000000000000007</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>5206838</v>
+        <v>4659079</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D16">
+        <v>9.8000000000000007</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -1013,82 +1018,82 @@
         <v>14</v>
       </c>
       <c r="I16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>4816613</v>
+        <v>4325032</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D17">
+        <v>9.8000000000000007</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G17" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I17" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>4314132</v>
+        <v>4588374</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D18">
+        <v>9.8000000000000007</v>
       </c>
       <c r="E18" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I18" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>3984667</v>
+        <v>2767962</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D19">
+        <v>9.6</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
         <v>12</v>
@@ -1100,27 +1105,27 @@
         <v>14</v>
       </c>
       <c r="I19" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>4142803</v>
+        <v>5109280</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D20">
+        <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1129,189 +1134,821 @@
         <v>14</v>
       </c>
       <c r="I20" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>4810448</v>
+        <v>4421458</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D21">
+        <v>9.3000000000000007</v>
       </c>
       <c r="E21" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H21" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I21" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>4740597</v>
+        <v>2203722</v>
       </c>
       <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s">
         <v>16</v>
       </c>
-      <c r="C22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" t="s">
-        <v>13</v>
-      </c>
       <c r="H22" t="s">
         <v>14</v>
       </c>
       <c r="I22" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>4477131</v>
+        <v>3143293</v>
       </c>
       <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" t="s">
         <v>16</v>
       </c>
-      <c r="C23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" t="s">
-        <v>13</v>
-      </c>
       <c r="H23" t="s">
         <v>14</v>
       </c>
       <c r="I23" t="s">
-        <v>28</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>3795588</v>
+      </c>
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24">
+        <v>8.9</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>4379479</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25">
+        <v>8.1</v>
+      </c>
+      <c r="E25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" t="s">
+        <v>10</v>
+      </c>
+      <c r="I25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>3591438</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26">
+        <v>9.1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>3520767</v>
+      </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>4570804</v>
+      </c>
+      <c r="B28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" t="s">
+        <v>10</v>
+      </c>
+      <c r="I28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>2750092</v>
+      </c>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29">
+        <v>9.6</v>
+      </c>
+      <c r="E29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>4299838</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30">
+        <v>9.4</v>
+      </c>
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" t="s">
+        <v>10</v>
+      </c>
+      <c r="I30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>4326805</v>
+      </c>
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31">
+        <v>9</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>4382854</v>
+      </c>
+      <c r="B32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>3428960</v>
+      </c>
+      <c r="B33" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33">
+        <v>9.5</v>
+      </c>
+      <c r="E33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>4490625</v>
+      </c>
+      <c r="B34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34">
+        <v>7.5</v>
+      </c>
+      <c r="E34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" t="s">
+        <v>10</v>
+      </c>
+      <c r="I34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>3981868</v>
+      </c>
+      <c r="B35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35">
+        <v>9</v>
+      </c>
+      <c r="E35" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>4277688</v>
+      </c>
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36">
+        <v>10</v>
+      </c>
+      <c r="E36" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" t="s">
+        <v>8</v>
+      </c>
+      <c r="G36" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" t="s">
+        <v>10</v>
+      </c>
+      <c r="I36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>4111461</v>
+      </c>
+      <c r="B37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37">
+        <v>10.1</v>
+      </c>
+      <c r="E37" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" t="s">
+        <v>8</v>
+      </c>
+      <c r="G37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H37" t="s">
+        <v>10</v>
+      </c>
+      <c r="I37" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>4097779</v>
+      </c>
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38">
+        <v>9.1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" t="s">
+        <v>8</v>
+      </c>
+      <c r="G38" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" t="s">
+        <v>10</v>
+      </c>
+      <c r="I38" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>4314860</v>
+      </c>
+      <c r="B39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39">
+        <v>8.5</v>
+      </c>
+      <c r="E39" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" t="s">
+        <v>10</v>
+      </c>
+      <c r="I39" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>4911676</v>
+      </c>
+      <c r="B40" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40">
+        <v>9</v>
+      </c>
+      <c r="E40" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" t="s">
+        <v>10</v>
+      </c>
+      <c r="I40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>4753716</v>
+      </c>
+      <c r="B41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41">
+        <v>8.6</v>
+      </c>
+      <c r="E41" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" t="s">
+        <v>9</v>
+      </c>
+      <c r="H41" t="s">
+        <v>10</v>
+      </c>
+      <c r="I41" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>4109237</v>
+      </c>
+      <c r="B42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42">
+        <v>9.1</v>
+      </c>
+      <c r="E42" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" t="s">
+        <v>10</v>
+      </c>
+      <c r="I42" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>3952121</v>
+      </c>
+      <c r="B43" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E43" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>2699654</v>
+      </c>
+      <c r="B44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44">
+        <v>11.4</v>
+      </c>
+      <c r="E44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>4071563</v>
+      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45">
+        <v>8.9</v>
+      </c>
+      <c r="E45" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAB8F01F-C0CC-443D-A91D-E2D43BE87FA9}">
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7CC170-1341-4BB9-89BA-32F4E1D07079}">
+  <dimension ref="A1:I45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="36.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="42.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>27</v>
+      <c r="I1" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>4826169</v>
+        <v>4296363</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>4553029</v>
+        <v>5208077</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -1320,30 +1957,30 @@
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>4034048</v>
+        <v>3520989</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -1352,24 +1989,24 @@
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>3999212</v>
+        <v>4035279</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
@@ -1378,85 +2015,85 @@
         <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>5212942</v>
+        <v>4033723</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>4460076</v>
+        <v>2811296</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>4489643</v>
+        <v>2716334</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -1468,140 +2105,140 @@
         <v>14</v>
       </c>
       <c r="I8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>4667047</v>
+        <v>4280394</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>4613005</v>
+        <v>5140263</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I10" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>5206838</v>
+        <v>3815749</v>
       </c>
       <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
         <v>16</v>
       </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
-      </c>
       <c r="H11" t="s">
         <v>14</v>
       </c>
       <c r="I11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>4300522</v>
+        <v>4795407</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I12" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>3635296</v>
+        <v>4571894</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
@@ -1610,85 +2247,85 @@
         <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>3984667</v>
+        <v>4286124</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I14" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>4142803</v>
+        <v>5105760</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>4276592</v>
+        <v>4659079</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -1700,82 +2337,82 @@
         <v>14</v>
       </c>
       <c r="I16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>4718808</v>
+        <v>4325032</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G17" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I17" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>4816613</v>
+        <v>4588374</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I18" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>4740597</v>
+        <v>2767962</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
         <v>12</v>
@@ -1787,27 +2424,27 @@
         <v>14</v>
       </c>
       <c r="I19" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>4001669</v>
+        <v>5109280</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1816,97 +2453,3509 @@
         <v>14</v>
       </c>
       <c r="I20" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>4314132</v>
+        <v>4421458</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
         <v>18</v>
       </c>
-      <c r="F21" t="s">
-        <v>12</v>
-      </c>
       <c r="G21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H21" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I21" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>4810448</v>
+        <v>2203722</v>
       </c>
       <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s">
         <v>16</v>
       </c>
-      <c r="C22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" t="s">
-        <v>13</v>
-      </c>
       <c r="H22" t="s">
         <v>14</v>
       </c>
       <c r="I22" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>4477131</v>
+        <v>3143293</v>
       </c>
       <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" t="s">
         <v>16</v>
       </c>
+      <c r="H23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>3795588</v>
+      </c>
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>4379479</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" t="s">
+        <v>10</v>
+      </c>
+      <c r="I25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>3591438</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>3520767</v>
+      </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>4570804</v>
+      </c>
+      <c r="B28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" t="s">
+        <v>10</v>
+      </c>
+      <c r="I28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>2750092</v>
+      </c>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>4299838</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" t="s">
+        <v>10</v>
+      </c>
+      <c r="I30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>4326805</v>
+      </c>
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>4382854</v>
+      </c>
+      <c r="B32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>3428960</v>
+      </c>
+      <c r="B33" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>4490625</v>
+      </c>
+      <c r="B34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" t="s">
+        <v>10</v>
+      </c>
+      <c r="I34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>3981868</v>
+      </c>
+      <c r="B35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>4277688</v>
+      </c>
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" t="s">
+        <v>8</v>
+      </c>
+      <c r="G36" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" t="s">
+        <v>10</v>
+      </c>
+      <c r="I36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>4111461</v>
+      </c>
+      <c r="B37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" t="s">
+        <v>38</v>
+      </c>
+      <c r="E37" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" t="s">
+        <v>8</v>
+      </c>
+      <c r="G37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H37" t="s">
+        <v>10</v>
+      </c>
+      <c r="I37" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>4097779</v>
+      </c>
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E38" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" t="s">
+        <v>8</v>
+      </c>
+      <c r="G38" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" t="s">
+        <v>10</v>
+      </c>
+      <c r="I38" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>4314860</v>
+      </c>
+      <c r="B39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" t="s">
+        <v>44</v>
+      </c>
+      <c r="E39" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" t="s">
+        <v>10</v>
+      </c>
+      <c r="I39" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>4911676</v>
+      </c>
+      <c r="B40" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" t="s">
+        <v>47</v>
+      </c>
+      <c r="E40" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" t="s">
+        <v>10</v>
+      </c>
+      <c r="I40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>4753716</v>
+      </c>
+      <c r="B41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" t="s">
+        <v>9</v>
+      </c>
+      <c r="H41" t="s">
+        <v>10</v>
+      </c>
+      <c r="I41" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>4109237</v>
+      </c>
+      <c r="B42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" t="s">
+        <v>37</v>
+      </c>
+      <c r="E42" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" t="s">
+        <v>10</v>
+      </c>
+      <c r="I42" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>3952121</v>
+      </c>
+      <c r="B43" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" t="s">
+        <v>48</v>
+      </c>
+      <c r="E43" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>2699654</v>
+      </c>
+      <c r="B44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" t="s">
+        <v>49</v>
+      </c>
+      <c r="E44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>4071563</v>
+      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" t="s">
+        <v>29</v>
+      </c>
+      <c r="E45" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB0AF8CB-130A-407C-8EC9-18E9C7631F46}">
+  <dimension ref="A1:J45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>4296363</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>11.2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>5208077</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>12.2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3520989</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4035279</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>9.5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>4033723</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>11.4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2811296</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>11.6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2716334</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>11.3</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>4280394</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>11.3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>5140263</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10">
+        <v>11.3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>3815749</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>4795407</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12">
+        <v>11.4</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>4571894</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13">
+        <v>12.1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>4286124</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14">
+        <v>9.1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>5105760</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15">
+        <v>11.6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>4659079</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>4325032</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17">
+        <v>10.7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>4588374</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18">
+        <v>10.9</v>
+      </c>
+      <c r="E18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>2767962</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19">
+        <v>11.6</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>5109280</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" t="s">
+        <v>23</v>
+      </c>
+      <c r="J20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>4421458</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>2203722</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22">
+        <v>11.7</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>3143293</v>
+      </c>
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
       <c r="C23" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" t="s">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="D23">
+        <v>12.1</v>
       </c>
       <c r="E23" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
         <v>12</v>
       </c>
       <c r="G23" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H23" t="s">
         <v>14</v>
       </c>
       <c r="I23" t="s">
-        <v>28</v>
+        <v>23</v>
+      </c>
+      <c r="J23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>3795588</v>
+      </c>
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24">
+        <v>9.5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>4379479</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25">
+        <v>9</v>
+      </c>
+      <c r="E25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" t="s">
+        <v>10</v>
+      </c>
+      <c r="I25" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>3591438</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26">
+        <v>11.9</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>3520767</v>
+      </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27">
+        <v>12.4</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>4570804</v>
+      </c>
+      <c r="B28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28">
+        <v>12.5</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" t="s">
+        <v>10</v>
+      </c>
+      <c r="I28" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>2750092</v>
+      </c>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29">
+        <v>12</v>
+      </c>
+      <c r="E29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" t="s">
+        <v>23</v>
+      </c>
+      <c r="J29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>4299838</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30">
+        <v>11.4</v>
+      </c>
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" t="s">
+        <v>10</v>
+      </c>
+      <c r="I30" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>4326805</v>
+      </c>
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31">
+        <v>11.9</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" t="s">
+        <v>23</v>
+      </c>
+      <c r="J31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>4382854</v>
+      </c>
+      <c r="B32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" t="s">
+        <v>23</v>
+      </c>
+      <c r="J32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>3428960</v>
+      </c>
+      <c r="B33" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33">
+        <v>11.8</v>
+      </c>
+      <c r="E33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33" t="s">
+        <v>23</v>
+      </c>
+      <c r="J33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>4490625</v>
+      </c>
+      <c r="B34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" t="s">
+        <v>10</v>
+      </c>
+      <c r="I34" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>3981868</v>
+      </c>
+      <c r="B35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>4277688</v>
+      </c>
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36">
+        <v>11.2</v>
+      </c>
+      <c r="E36" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" t="s">
+        <v>8</v>
+      </c>
+      <c r="G36" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" t="s">
+        <v>10</v>
+      </c>
+      <c r="I36" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>4111461</v>
+      </c>
+      <c r="B37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" t="s">
+        <v>8</v>
+      </c>
+      <c r="G37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H37" t="s">
+        <v>10</v>
+      </c>
+      <c r="I37" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>4097779</v>
+      </c>
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38">
+        <v>11.3</v>
+      </c>
+      <c r="E38" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" t="s">
+        <v>8</v>
+      </c>
+      <c r="G38" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" t="s">
+        <v>10</v>
+      </c>
+      <c r="I38" t="s">
+        <v>23</v>
+      </c>
+      <c r="J38" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>4314860</v>
+      </c>
+      <c r="B39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" t="s">
+        <v>10</v>
+      </c>
+      <c r="I39" t="s">
+        <v>23</v>
+      </c>
+      <c r="J39" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>4911676</v>
+      </c>
+      <c r="B40" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40">
+        <v>11.3</v>
+      </c>
+      <c r="E40" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" t="s">
+        <v>10</v>
+      </c>
+      <c r="I40" t="s">
+        <v>23</v>
+      </c>
+      <c r="J40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>4753716</v>
+      </c>
+      <c r="B41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41">
+        <v>11.7</v>
+      </c>
+      <c r="E41" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" t="s">
+        <v>9</v>
+      </c>
+      <c r="H41" t="s">
+        <v>10</v>
+      </c>
+      <c r="I41" t="s">
+        <v>23</v>
+      </c>
+      <c r="J41" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>4109237</v>
+      </c>
+      <c r="B42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" t="s">
+        <v>10</v>
+      </c>
+      <c r="I42" t="s">
+        <v>23</v>
+      </c>
+      <c r="J42" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>3952121</v>
+      </c>
+      <c r="B43" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43">
+        <v>11.8</v>
+      </c>
+      <c r="E43" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" t="s">
+        <v>23</v>
+      </c>
+      <c r="J43" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>2699654</v>
+      </c>
+      <c r="B44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44">
+        <v>11.7</v>
+      </c>
+      <c r="E44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" t="s">
+        <v>23</v>
+      </c>
+      <c r="J44" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>4071563</v>
+      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45">
+        <v>11.7</v>
+      </c>
+      <c r="E45" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" t="s">
+        <v>23</v>
+      </c>
+      <c r="J45" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:I45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="42.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>4296363</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>10.4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>5208077</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>10.5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3520989</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>11.9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4035279</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>10.4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>4033723</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>11.3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2811296</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>9.4700000000000006</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2716334</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>11.8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>4280394</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>11.3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>5140263</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>3815749</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>10.95</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>4795407</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12">
+        <v>10.9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>4571894</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13">
+        <v>10.4</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>4286124</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14">
+        <v>8.4</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>5105760</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15">
+        <v>11.4</v>
+      </c>
+      <c r="E15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>4659079</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16">
+        <v>10.3</v>
+      </c>
+      <c r="E16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>4325032</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17">
+        <v>9.1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>4588374</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>2767962</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19">
+        <v>11.5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>5109280</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20">
+        <v>11.6</v>
+      </c>
+      <c r="E20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>4421458</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21">
+        <v>10.5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>2203722</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22">
+        <v>10.6</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>3143293</v>
+      </c>
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23">
+        <v>12.07</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>3795588</v>
+      </c>
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24">
+        <v>10.8</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" t="s">
+        <v>10</v>
+      </c>
+      <c r="I24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>4379479</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25">
+        <v>6.9</v>
+      </c>
+      <c r="E25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" t="s">
+        <v>10</v>
+      </c>
+      <c r="I25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>3591438</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26">
+        <v>11.8</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>3520767</v>
+      </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27">
+        <v>11.6</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>4570804</v>
+      </c>
+      <c r="B28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28">
+        <v>10.6</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" t="s">
+        <v>10</v>
+      </c>
+      <c r="I28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>2750092</v>
+      </c>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29">
+        <v>10.9</v>
+      </c>
+      <c r="E29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>4299838</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30">
+        <v>10.6</v>
+      </c>
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" t="s">
+        <v>10</v>
+      </c>
+      <c r="I30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>4326805</v>
+      </c>
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>4382854</v>
+      </c>
+      <c r="B32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" t="s">
+        <v>10</v>
+      </c>
+      <c r="I32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>3428960</v>
+      </c>
+      <c r="B33" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33">
+        <v>10.4</v>
+      </c>
+      <c r="E33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s">
+        <v>10</v>
+      </c>
+      <c r="I33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>4490625</v>
+      </c>
+      <c r="B34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34">
+        <v>10.3</v>
+      </c>
+      <c r="E34" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" t="s">
+        <v>10</v>
+      </c>
+      <c r="I34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>3981868</v>
+      </c>
+      <c r="B35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35">
+        <v>11.4</v>
+      </c>
+      <c r="E35" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" t="s">
+        <v>10</v>
+      </c>
+      <c r="I35" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>4277688</v>
+      </c>
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36">
+        <v>10.9</v>
+      </c>
+      <c r="E36" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" t="s">
+        <v>8</v>
+      </c>
+      <c r="G36" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" t="s">
+        <v>10</v>
+      </c>
+      <c r="I36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>4111461</v>
+      </c>
+      <c r="B37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37">
+        <v>11.2</v>
+      </c>
+      <c r="E37" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" t="s">
+        <v>8</v>
+      </c>
+      <c r="G37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H37" t="s">
+        <v>10</v>
+      </c>
+      <c r="I37" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>4097779</v>
+      </c>
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" t="s">
+        <v>8</v>
+      </c>
+      <c r="G38" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" t="s">
+        <v>10</v>
+      </c>
+      <c r="I38" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>4314860</v>
+      </c>
+      <c r="B39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39">
+        <v>10.7</v>
+      </c>
+      <c r="E39" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" t="s">
+        <v>10</v>
+      </c>
+      <c r="I39" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>4911676</v>
+      </c>
+      <c r="B40" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40">
+        <v>10.7</v>
+      </c>
+      <c r="E40" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" t="s">
+        <v>10</v>
+      </c>
+      <c r="I40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>4753716</v>
+      </c>
+      <c r="B41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41">
+        <v>10.7</v>
+      </c>
+      <c r="E41" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" t="s">
+        <v>9</v>
+      </c>
+      <c r="H41" t="s">
+        <v>10</v>
+      </c>
+      <c r="I41" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>4109237</v>
+      </c>
+      <c r="B42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42">
+        <v>10.3</v>
+      </c>
+      <c r="E42" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" t="s">
+        <v>10</v>
+      </c>
+      <c r="I42" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>3952121</v>
+      </c>
+      <c r="B43" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>2699654</v>
+      </c>
+      <c r="B44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44">
+        <v>11.6</v>
+      </c>
+      <c r="E44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>4071563</v>
+      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45">
+        <v>11.4</v>
+      </c>
+      <c r="E45" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>